--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé rentre du marché avec papa. Dans le panier, il y a des carottes orange. Papa les lave. Il coupe une petite carotte. Noé s'assoit à table. Papa dit : tu peux goûter. Une petite portion, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. Il dit à papa : c'est sucré et croquant. Papa sourit. Merci d'avoir goûté, dit papa. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Papa range le reste. Noé a goûté. Il a dit le goût.</t>
+          <t>Noé rentre du marché avec papa. Dans le panier, il y a des carottes orange. Papa les lave. Il coupe une petite carotte. Noé s'assoit à table. Tu peux goûter. Une petite portion, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. Il dit à papa : c'est sucré et croquant. Papa sourit. Merci d'avoir goûté, dit papa. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Papa range le reste. Noé a goûté. Il a dit le goût.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rentre du marché avec papa. Dans le panier, il y a des carottes orange. Papa les lave. Il coupe une petite carotte. Noé s'assoit à table.
+papa|Tu peux goûter.
+narrateur|Une petite portion, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. Il dit à papa : c'est sucré et croquant. Papa sourit. Merci d'avoir goûté, dit papa. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Papa range le reste. Noé a goûté. Il a dit le goût.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Noé goûte la carotte. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1661,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1824,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Noé range sa chaise. La carotte reste à sa place. Merci, dit Noé.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1991,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2014,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2031,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Une petite portion, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. Il dit à papa : c'est sucré et croquant. Papa sourit. Merci d'avoir goûté, dit papa. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Papa range le reste. Noé a goûté. Il a dit le goût.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Noé goûte la carotte. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1666,6 +1673,7 @@
           <t>narrateur|Noé a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1837,7 @@
           <t>narrateur|Noé range sa chaise. La carotte reste à sa place. Merci, dit Noé.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1996,6 +2005,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2014,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2038,6 +2048,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2076,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2239,6 +2263,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Noé rentre du marché et aide papa à poser le panier. Une carotte roule ; il la rattrape. Papa propose alors une petite bouchée : Noé goûte, nomme le goût, sans tout finir.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé rentre du marché avec papa. Dans le panier, il y a des carottes orange. Papa les lave. Il coupe une petite carotte. Noé s'assoit à table. Tu peux goûter. Une petite portion, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. Il dit à papa : c'est sucré et croquant. Papa sourit. Merci d'avoir goûté, dit papa. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Papa range le reste. Noé a goûté. Il a dit le goût.</t>
+          <t>Noé rentre du marché avec papa. Il aide à poser le panier sur la table. Le panier est plein. Alors une carotte orange roule. Elle part vers le bord. Noé ouvre les yeux. Il est surpris. Il avance les deux mains. Alors il rattrape la carotte. Noé sourit. La carotte est dans ses mains. Elle est lisse. Elle est froide. Elle sent le marché. Bien attrapé. On range ensemble. Noé pose la carotte près de l'évier. Papa lave la carotte. Il coupe une petite portion. Juste une petite portion. Il la pose dans l'assiette de Noé. Noé s'assoit à table, près de papa. Papa s'assoit aussi. Tu peux goûter. Une petite bouchée, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. C'est sucré. C'est croquant, papa. Merci d'avoir goûté. Tu as nommé le goût. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Puis il aide encore. Il range une pomme. Papa range le reste. Le panier est plus léger. La carotte a roulé. Noé l'a rattrapée. Il a goûté. Il a nommé le goût.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,27 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé rentre du marché avec papa. Dans le panier, il y a des carottes orange. Papa les lave. Il coupe une petite carotte. Noé s'assoit à table.
-papa|Tu peux goûter.
-narrateur|Une petite portion, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. Il dit à papa : c'est sucré et croquant. Papa sourit. Merci d'avoir goûté, dit papa. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Papa range le reste. Noé a goûté. Il a dit le goût.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Noé rentre du marché avec papa. Il aide à poser le panier sur la table.
+narrateur|Le panier est plein. Alors une carotte orange roule. Elle part vers le bord.
+narrateur|Noé ouvre les yeux. Il est surpris. Il avance les deux mains. Alors il rattrape la carotte.
+narrateur|Noé sourit. La carotte est dans ses mains. Elle est lisse. Elle est froide. Elle sent le marché.
+papa|Bien attrapé. On range ensemble.
+narrateur|Noé pose la carotte près de l'évier. Papa lave la carotte. Il coupe une petite portion. Juste une petite portion. Il la pose dans l'assiette de Noé.
+narrateur|Noé s'assoit à table, près de papa. Papa s'assoit aussi.
+papa|Tu peux goûter. Une petite bouchée, c'est assez.
+narrateur|Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût.
+enfant-m|C'est sucré. C'est croquant, papa.
+papa|Merci d'avoir goûté. Tu as nommé le goût.
+narrateur|La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau.
+narrateur|Puis il aide encore. Il range une pomme. Papa range le reste. Le panier est plus léger.
+narrateur|La carotte a roulé. Noé l'a rattrapée. Il a goûté. Il a nommé le goût.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>panier,carotte_roule</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,7 +1528,6 @@
           <t>narrateur|Noé goûte la carotte. Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,7 +1552,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
+          <t>Noé a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là. Le panier est rangé.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1670,10 +1696,11 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Noé a goûté. Il a nommé le goût.
+papa|Une petite portion, c'est assez.
+narrateur|Papa est là. Le panier est rangé.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1698,7 +1725,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé range sa chaise. La carotte reste à sa place. Merci, dit Noé.</t>
+          <t>Noé range sa chaise. Le panier est à sa place. La carotte reste dans l'assiette. Merci, papa.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1834,10 +1861,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé range sa chaise. La carotte reste à sa place. Merci, dit Noé.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Noé range sa chaise. Le panier est à sa place. La carotte reste dans l'assiette.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>chaise</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,7 +2037,6 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2062,6 +2093,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La petite carotte de Noé</t>
+          <t>La carotte qui s'échappe</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Noé rentre du marché et aide papa à poser le panier. Une carotte roule ; il la rattrape. Papa propose alors une petite bouchée : Noé goûte, nomme le goût, sans tout finir.</t>
+          <t>Une carotte s'échappe du panier. Noé la rattrape. Papa lui tend un petit morceau. Noé goûte.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé rentre du marché avec papa. Il aide à poser le panier sur la table. Le panier est plein. Alors une carotte orange roule. Elle part vers le bord. Noé ouvre les yeux. Il est surpris. Il avance les deux mains. Alors il rattrape la carotte. Noé sourit. La carotte est dans ses mains. Elle est lisse. Elle est froide. Elle sent le marché. Bien attrapé. On range ensemble. Noé pose la carotte près de l'évier. Papa lave la carotte. Il coupe une petite portion. Juste une petite portion. Il la pose dans l'assiette de Noé. Noé s'assoit à table, près de papa. Papa s'assoit aussi. Tu peux goûter. Une petite bouchée, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. C'est sucré. C'est croquant, papa. Merci d'avoir goûté. Tu as nommé le goût. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Puis il aide encore. Il range une pomme. Papa range le reste. Le panier est plus léger. La carotte a roulé. Noé l'a rattrapée. Il a goûté. Il a nommé le goût.</t>
+          <t>Noé rentre du marché avec papa. Ils posent le panier sur la table. Le panier est plein. Il penche. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Noé se baisse. Il avance les deux mains. Il la rattrape. Bien attrapé, Noé. La carotte est lisse et froide. Elle sent le marché. Papa lave la carotte. Il coupe un petit morceau. Tu veux goûter ? Noé met le morceau dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1324,20 +1324,26 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé rentre du marché avec papa. Il aide à poser le panier sur la table.
-narrateur|Le panier est plein. Alors une carotte orange roule. Elle part vers le bord.
-narrateur|Noé ouvre les yeux. Il est surpris. Il avance les deux mains. Alors il rattrape la carotte.
-narrateur|Noé sourit. La carotte est dans ses mains. Elle est lisse. Elle est froide. Elle sent le marché.
-papa|Bien attrapé. On range ensemble.
-narrateur|Noé pose la carotte près de l'évier. Papa lave la carotte. Il coupe une petite portion. Juste une petite portion. Il la pose dans l'assiette de Noé.
-narrateur|Noé s'assoit à table, près de papa. Papa s'assoit aussi.
-papa|Tu peux goûter. Une petite bouchée, c'est assez.
-narrateur|Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût.
-enfant-m|C'est sucré. C'est croquant, papa.
-papa|Merci d'avoir goûté. Tu as nommé le goût.
-narrateur|La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau.
-narrateur|Puis il aide encore. Il range une pomme. Papa range le reste. Le panier est plus léger.
-narrateur|La carotte a roulé. Noé l'a rattrapée. Il a goûté. Il a nommé le goût.</t>
+          <t>narrateur|Noé rentre du marché avec papa.
+narrateur|Ils posent le panier sur la table.
+narrateur|Le panier est plein.
+narrateur|Il penche.
+narrateur|Une carotte orange s'échappe.
+narrateur|Elle roule vers le bord.
+enfant-m|Elle part !
+narrateur|Elle tombe par terre.
+narrateur|Elle roule sous la table.
+narrateur|Noé se baisse.
+narrateur|Il avance les deux mains.
+narrateur|Il la rattrape.
+papa|Bien attrapé, Noé.
+narrateur|La carotte est lisse et froide.
+narrateur|Elle sent le marché.
+narrateur|Papa lave la carotte.
+narrateur|Il coupe un petit morceau.
+papa|Tu veux goûter ?
+narrateur|Noé met le morceau dans sa bouche.
+narrateur|Il goûte.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1369,7 +1375,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé goûte la carotte. Que fait-il ?</t>
+          <t>Noé goûte. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1525,9 +1531,11 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé goûte la carotte. Que fait-il ?</t>
-        </is>
-      </c>
+          <t>narrateur|Noé goûte.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1552,7 +1560,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé a goûté. Il a nommé le goût. Une petite portion, c'est assez. Papa est là. Le panier est rangé.</t>
+          <t>Noé mâche. Ça croque. C'est sucré, papa. C'est croquant. Oui. Un bout reste dans l'assiette.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1696,11 +1704,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé a goûté. Il a nommé le goût.
-papa|Une petite portion, c'est assez.
-narrateur|Papa est là. Le panier est rangé.</t>
-        </is>
-      </c>
+          <t>narrateur|Noé mâche.
+narrateur|Ça croque.
+enfant-m|C'est sucré, papa.
+enfant-m|C'est croquant.
+papa|Oui.
+narrateur|Un bout reste dans l'assiette.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1725,7 +1737,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé range sa chaise. Le panier est à sa place. La carotte reste dans l'assiette. Merci, papa.</t>
+          <t>Noé pose le morceau. Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. On range le panier. La carotte ne s'échappe plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1861,15 +1873,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé range sa chaise. Le panier est à sa place. La carotte reste dans l'assiette.
-enfant-m|Merci, papa.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>chaise</t>
-        </is>
-      </c>
+          <t>narrateur|Noé pose le morceau.
+narrateur|Il boit une gorgée d'eau.
+narrateur|Le reste peut attendre.
+enfant-m|Merci, papa.
+narrateur|On range le panier.
+narrateur|La carotte ne s'échappe plus.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1894,7 +1906,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Noé a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2034,9 +2046,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
+          <t>narrateur|Noé a encore le croquant dans la bouche.
+enfant-m|C'était sucré.
+narrateur|Un petit morceau a suffi.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2055,7 +2071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2098,6 +2114,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -602,6 +602,11 @@
           <t>secondary_lessons</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>SAN.ALI.002</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -841,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une carotte s'échappe du panier. Noé la rattrape. Papa lui tend un petit morceau. Noé goûte.</t>
+          <t>Une carotte s'échappe du panier. Noé la rattrape. Il s'assoit avec papa. Papa lui tend un petit morceau. Noé goûte.</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé rentre du marché avec papa. Ils posent le panier sur la table. Le panier est plein. Il penche. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Noé se baisse. Il avance les deux mains. Il la rattrape. Bien attrapé, Noé. La carotte est lisse et froide. Elle sent le marché. Papa lave la carotte. Il coupe un petit morceau. Tu veux goûter ? Noé met le morceau dans sa bouche. Il goûte.</t>
+          <t>Noé rentre du marché avec papa. Ils portent le panier, à deux. Ils arrivent dans la cuisine. Ils posent le panier sur la table. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Elle tourne près d'une chaise. Noé se baisse. Il avance les deux mains. La carotte roule encore. Noé la suit. Il avance encore. Il la rattrape. Elle est dans ses mains. Bien attrapé, Noé. La carotte est lisse et froide. Elle sent le marché. Noé la sent encore. Un peu la terre. Un peu le soleil. Noé la montre à papa. Papa lave la carotte. L'eau coule. Noé attend près de lui. Papa coupe un petit morceau. Viens t'asseoir. Noé va vers sa chaise. Il s'assoit à table. Papa s'assoit aussi. On est ensemble. Noé est bien assis. Il pose les mains sur la table. Il regarde le petit morceau. Le morceau est orange. Il brille un peu. Tu veux goûter ? Noé met le morceau dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,22 +1330,45 @@
       <c r="AW2" t="inlineStr">
         <is>
           <t>narrateur|Noé rentre du marché avec papa.
+narrateur|Ils portent le panier, à deux.
+narrateur|Ils arrivent dans la cuisine.
 narrateur|Ils posent le panier sur la table.
 narrateur|Le panier est plein.
-narrateur|Il penche.
+narrateur|Il penche un peu.
 narrateur|Une carotte orange s'échappe.
 narrateur|Elle roule vers le bord.
 enfant-m|Elle part !
 narrateur|Elle tombe par terre.
 narrateur|Elle roule sous la table.
+narrateur|Elle tourne près d'une chaise.
 narrateur|Noé se baisse.
 narrateur|Il avance les deux mains.
+narrateur|La carotte roule encore.
+narrateur|Noé la suit.
+narrateur|Il avance encore.
 narrateur|Il la rattrape.
+narrateur|Elle est dans ses mains.
 papa|Bien attrapé, Noé.
 narrateur|La carotte est lisse et froide.
 narrateur|Elle sent le marché.
+narrateur|Noé la sent encore.
+narrateur|Un peu la terre.
+narrateur|Un peu le soleil.
+narrateur|Noé la montre à papa.
 narrateur|Papa lave la carotte.
-narrateur|Il coupe un petit morceau.
+narrateur|L'eau coule.
+narrateur|Noé attend près de lui.
+narrateur|Papa coupe un petit morceau.
+papa|Viens t'asseoir.
+narrateur|Noé va vers sa chaise.
+narrateur|Il s'assoit à table.
+narrateur|Papa s'assoit aussi.
+papa|On est ensemble.
+narrateur|Noé est bien assis.
+narrateur|Il pose les mains sur la table.
+narrateur|Il regarde le petit morceau.
+narrateur|Le morceau est orange.
+narrateur|Il brille un peu.
 papa|Tu veux goûter ?
 narrateur|Noé met le morceau dans sa bouche.
 narrateur|Il goûte.</t>
@@ -1560,7 +1588,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé mâche. Ça croque. C'est sucré, papa. C'est croquant. Oui. Un bout reste dans l'assiette.</t>
+          <t>Noé mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Noé est encore assis. Un bout reste dans l'assiette.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1706,9 +1734,12 @@
         <is>
           <t>narrateur|Noé mâche.
 narrateur|Ça croque.
+narrateur|Il mâche encore.
 enfant-m|C'est sucré, papa.
 enfant-m|C'est croquant.
 papa|Oui.
+papa|Sucré et croquant.
+narrateur|Noé est encore assis.
 narrateur|Un bout reste dans l'assiette.</t>
         </is>
       </c>
@@ -1737,7 +1768,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé pose le morceau. Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. On range le panier. La carotte ne s'échappe plus.</t>
+          <t>Noé pose le morceau. Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. Ils restent un moment, à table. Noé regarde le panier. Puis on range le panier. Noé aide. La cuisine est calme. Noé ne se lève pas tout de suite. Il reste avec papa. Le bout orange attend. La carotte ne s'échappe plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1877,7 +1908,14 @@
 narrateur|Il boit une gorgée d'eau.
 narrateur|Le reste peut attendre.
 enfant-m|Merci, papa.
-narrateur|On range le panier.
+narrateur|Ils restent un moment, à table.
+narrateur|Noé regarde le panier.
+narrateur|Puis on range le panier.
+narrateur|Noé aide.
+narrateur|La cuisine est calme.
+narrateur|Noé ne se lève pas tout de suite.
+narrateur|Il reste avec papa.
+narrateur|Le bout orange attend.
 narrateur|La carotte ne s'échappe plus.</t>
         </is>
       </c>
@@ -1906,7 +1944,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Noé a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. L'histoire est finie.</t>
+          <t>Noé a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. On était assis, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2049,6 +2087,7 @@
           <t>narrateur|Noé a encore le croquant dans la bouche.
 enfant-m|C'était sucré.
 narrateur|Un petit morceau a suffi.
+papa|On était assis, ensemble.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -2071,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2121,6 +2160,27 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé rentre du marché avec papa. Ils portent le panier, à deux. Ils arrivent dans la cuisine. Ils posent le panier sur la table. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Elle tourne près d'une chaise. Noé se baisse. Il avance les deux mains. La carotte roule encore. Noé la suit. Il avance encore. Il la rattrape. Elle est dans ses mains. Bien attrapé, Noé. La carotte est lisse et froide. Elle sent le marché. Noé la sent encore. Un peu la terre. Un peu le soleil. Noé la montre à papa. Papa lave la carotte. L'eau coule. Noé attend près de lui. Papa coupe un petit morceau. Viens t'asseoir. Noé va vers sa chaise. Il s'assoit à table. Papa s'assoit aussi. On est ensemble. Noé est bien assis. Il pose les mains sur la table. Il regarde le petit morceau. Le morceau est orange. Il brille un peu. Tu veux goûter ? Noé met le morceau dans sa bouche. Il goûte.</t>
+          <t>Noé rentre du marché avec papa. Ils portent le panier, à deux. Ils arrivent dans la cuisine. On pose le panier sur la table ? Ils posent le panier sur la table. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Elle tourne près d'une chaise. Tu peux la rattraper, Noé. Noé se baisse. Il avance les deux mains. La carotte roule encore. Noé la suit. Il avance encore. Il la rattrape. Elle est dans ses mains. Bravo, Noé ! Bien attrapé. Tu as fait du bon travail. La carotte est lisse et froide. Elle sent le marché. Ça sent le marché, papa. Oui. Un peu la terre. Un peu le soleil. Tu la poses près de l'évier ? Noé la montre à papa. Papa lave la carotte. L'eau coule. On la lave ensemble. Noé attend près de lui. Papa coupe un petit morceau. Viens t'asseoir. Noé va vers sa chaise. Il s'assoit à table. Papa s'assoit aussi. Bravo. Tu es bien assis. On est ensemble. Noé pose les mains sur la table. Il regarde le petit morceau. Le morceau est orange. Il brille un peu. Tu veux goûter ? Noé met le morceau dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1332,6 +1332,7 @@
           <t>narrateur|Noé rentre du marché avec papa.
 narrateur|Ils portent le panier, à deux.
 narrateur|Ils arrivent dans la cuisine.
+papa|On pose le panier sur la table ?
 narrateur|Ils posent le panier sur la table.
 narrateur|Le panier est plein.
 narrateur|Il penche un peu.
@@ -1341,6 +1342,7 @@
 narrateur|Elle tombe par terre.
 narrateur|Elle roule sous la table.
 narrateur|Elle tourne près d'une chaise.
+papa|Tu peux la rattraper, Noé.
 narrateur|Noé se baisse.
 narrateur|Il avance les deux mains.
 narrateur|La carotte roule encore.
@@ -1348,24 +1350,27 @@
 narrateur|Il avance encore.
 narrateur|Il la rattrape.
 narrateur|Elle est dans ses mains.
-papa|Bien attrapé, Noé.
+papa|Bravo, Noé !
+papa|Bien attrapé.
+papa|Tu as fait du bon travail.
 narrateur|La carotte est lisse et froide.
 narrateur|Elle sent le marché.
-narrateur|Noé la sent encore.
-narrateur|Un peu la terre.
-narrateur|Un peu le soleil.
+enfant-m|Ça sent le marché, papa.
+papa|Oui. Un peu la terre. Un peu le soleil.
+papa|Tu la poses près de l'évier ?
 narrateur|Noé la montre à papa.
 narrateur|Papa lave la carotte.
 narrateur|L'eau coule.
+papa|On la lave ensemble.
 narrateur|Noé attend près de lui.
 narrateur|Papa coupe un petit morceau.
 papa|Viens t'asseoir.
 narrateur|Noé va vers sa chaise.
 narrateur|Il s'assoit à table.
 narrateur|Papa s'assoit aussi.
+papa|Bravo. Tu es bien assis.
 papa|On est ensemble.
-narrateur|Noé est bien assis.
-narrateur|Il pose les mains sur la table.
+narrateur|Noé pose les mains sur la table.
 narrateur|Il regarde le petit morceau.
 narrateur|Le morceau est orange.
 narrateur|Il brille un peu.
@@ -1588,7 +1593,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Noé est encore assis. Un bout reste dans l'assiette.</t>
+          <t>Noé mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Bravo. Tu as nommé le goût. C'est du bon travail. Un bout reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1737,10 +1742,11 @@
 narrateur|Il mâche encore.
 enfant-m|C'est sucré, papa.
 enfant-m|C'est croquant.
-papa|Oui.
-papa|Sucré et croquant.
-narrateur|Noé est encore assis.
-narrateur|Un bout reste dans l'assiette.</t>
+papa|Oui. Sucré et croquant.
+papa|Bravo. Tu as nommé le goût.
+papa|C'est du bon travail.
+narrateur|Un bout reste dans l'assiette.
+papa|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1768,7 +1774,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé pose le morceau. Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. Ils restent un moment, à table. Noé regarde le panier. Puis on range le panier. Noé aide. La cuisine est calme. Noé ne se lève pas tout de suite. Il reste avec papa. Le bout orange attend. La carotte ne s'échappe plus.</t>
+          <t>Noé pose le morceau. Tu veux un peu d'eau ? Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. Merci, Noé. On range le panier, maintenant ? Oui. Noé aide. Tu as fini de ranger le panier ? Oui, papa. Bravo. Tu as bien aidé. La cuisine est calme. On reste un moment à table ? Noé reste avec papa. Le bout orange attend. La carotte ne s'échappe plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1905,16 +1911,20 @@
       <c r="AW5" t="inlineStr">
         <is>
           <t>narrateur|Noé pose le morceau.
+papa|Tu veux un peu d'eau ?
 narrateur|Il boit une gorgée d'eau.
-narrateur|Le reste peut attendre.
+papa|Le reste peut attendre.
 enfant-m|Merci, papa.
-narrateur|Ils restent un moment, à table.
-narrateur|Noé regarde le panier.
-narrateur|Puis on range le panier.
+papa|Merci, Noé.
+papa|On range le panier, maintenant ?
+enfant-m|Oui.
 narrateur|Noé aide.
+papa|Tu as fini de ranger le panier ?
+enfant-m|Oui, papa.
+papa|Bravo. Tu as bien aidé.
 narrateur|La cuisine est calme.
-narrateur|Noé ne se lève pas tout de suite.
-narrateur|Il reste avec papa.
+papa|On reste un moment à table ?
+narrateur|Noé reste avec papa.
 narrateur|Le bout orange attend.
 narrateur|La carotte ne s'échappe plus.</t>
         </is>
@@ -1944,7 +1954,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Noé a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. On était assis, ensemble. L'histoire est finie.</t>
+          <t>Noé a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. Bravo, Noé. On était assis, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2086,7 +2096,8 @@
         <is>
           <t>narrateur|Noé a encore le croquant dans la bouche.
 enfant-m|C'était sucré.
-narrateur|Un petit morceau a suffi.
+papa|Un petit morceau a suffi.
+papa|Bravo, Noé.
 papa|On était assis, ensemble.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -2110,7 +2121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2181,6 +2192,13 @@
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
         </is>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -846,7 +846,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Une carotte s'échappe du panier. Noé la rattrape. Il s'assoit avec papa. Papa lui tend un petit morceau. Noé goûte.</t>
+          <t>Le marché sent la terre mouillée. Une carotte s'échappe du panier. Amir la rattrape. Il s'assoit avec papa. Il goûte un petit morceau.</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Noé rentre du marché avec papa. Ils portent le panier, à deux. Ils arrivent dans la cuisine. On pose le panier sur la table ? Ils posent le panier sur la table. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Elle tourne près d'une chaise. Tu peux la rattraper, Noé. Noé se baisse. Il avance les deux mains. La carotte roule encore. Noé la suit. Il avance encore. Il la rattrape. Elle est dans ses mains. Bravo, Noé ! Bien attrapé. Tu as fait du bon travail. La carotte est lisse et froide. Elle sent le marché. Ça sent le marché, papa. Oui. Un peu la terre. Un peu le soleil. Tu la poses près de l'évier ? Noé la montre à papa. Papa lave la carotte. L'eau coule. On la lave ensemble. Noé attend près de lui. Papa coupe un petit morceau. Viens t'asseoir. Noé va vers sa chaise. Il s'assoit à table. Papa s'assoit aussi. Bravo. Tu es bien assis. On est ensemble. Noé pose les mains sur la table. Il regarde le petit morceau. Le morceau est orange. Il brille un peu. Tu veux goûter ? Noé met le morceau dans sa bouche. Il goûte.</t>
+          <t>Ceci est l'histoire d'un petit panier. Le panier rentre du marché. Le village est encore tout frais. Il a plu, tout à l'heure. Les toits brillent. Amir marche avec papa. Leurs chaussures font clap, clap. Le panier est lourd, un peu. On le porte à deux ? Oui, papa. Ils arrivent dans la cuisine. L'évier sent le citron. On pose le panier sur la table ? Ils posent le panier. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Tu peux la rattraper, Amir. Amir se baisse. Il avance les deux mains. La carotte roule encore. Amir la suit. Il la rattrape. Elle est dans ses mains. Bravo, Amir ! Bien attrapé. Tu as fait du bon travail. La carotte est lisse et froide. Elle sent le marché. Ça sent le marché, papa. Oui. Un peu la terre. Un peu le soleil. Tu la poses près de l'évier ? Papa lave la carotte. L'eau coule. On la lave ensemble. Papa coupe un petit morceau. Viens t'asseoir. Amir s'assoit à table. Papa s'assoit aussi. Bravo. Tu es bien assis. On est ensemble. Le morceau est orange. Il brille un peu. Tu veux goûter ? Amir met le morceau dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1329,11 +1329,20 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Noé rentre du marché avec papa.
-narrateur|Ils portent le panier, à deux.
+          <t>narrateur|Ceci est l'histoire d'un petit panier.
+narrateur|Le panier rentre du marché.
+narrateur|Le village est encore tout frais.
+narrateur|Il a plu, tout à l'heure.
+narrateur|Les toits brillent.
+narrateur|Amir marche avec papa.
+narrateur|Leurs chaussures font clap, clap.
+narrateur|Le panier est lourd, un peu.
+papa|On le porte à deux ?
+enfant-m|Oui, papa.
 narrateur|Ils arrivent dans la cuisine.
+narrateur|L'évier sent le citron.
 papa|On pose le panier sur la table ?
-narrateur|Ils posent le panier sur la table.
+narrateur|Ils posent le panier.
 narrateur|Le panier est plein.
 narrateur|Il penche un peu.
 narrateur|Une carotte orange s'échappe.
@@ -1341,16 +1350,14 @@
 enfant-m|Elle part !
 narrateur|Elle tombe par terre.
 narrateur|Elle roule sous la table.
-narrateur|Elle tourne près d'une chaise.
-papa|Tu peux la rattraper, Noé.
-narrateur|Noé se baisse.
+papa|Tu peux la rattraper, Amir.
+narrateur|Amir se baisse.
 narrateur|Il avance les deux mains.
 narrateur|La carotte roule encore.
-narrateur|Noé la suit.
-narrateur|Il avance encore.
+narrateur|Amir la suit.
 narrateur|Il la rattrape.
 narrateur|Elle est dans ses mains.
-papa|Bravo, Noé !
+papa|Bravo, Amir !
 papa|Bien attrapé.
 papa|Tu as fait du bon travail.
 narrateur|La carotte est lisse et froide.
@@ -1358,24 +1365,19 @@
 enfant-m|Ça sent le marché, papa.
 papa|Oui. Un peu la terre. Un peu le soleil.
 papa|Tu la poses près de l'évier ?
-narrateur|Noé la montre à papa.
 narrateur|Papa lave la carotte.
 narrateur|L'eau coule.
 papa|On la lave ensemble.
-narrateur|Noé attend près de lui.
 narrateur|Papa coupe un petit morceau.
 papa|Viens t'asseoir.
-narrateur|Noé va vers sa chaise.
-narrateur|Il s'assoit à table.
+narrateur|Amir s'assoit à table.
 narrateur|Papa s'assoit aussi.
 papa|Bravo. Tu es bien assis.
 papa|On est ensemble.
-narrateur|Noé pose les mains sur la table.
-narrateur|Il regarde le petit morceau.
 narrateur|Le morceau est orange.
 narrateur|Il brille un peu.
 papa|Tu veux goûter ?
-narrateur|Noé met le morceau dans sa bouche.
+narrateur|Amir met le morceau dans sa bouche.
 narrateur|Il goûte.</t>
         </is>
       </c>
@@ -1408,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Noé goûte. Que fait-il ?</t>
+          <t>Amir goûte. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1564,7 +1566,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Noé goûte.
+          <t>narrateur|Amir goûte.
 narrateur|Que fait-il ?</t>
         </is>
       </c>
@@ -1593,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Bravo. Tu as nommé le goût. C'est du bon travail. Un bout reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
+          <t>Amir mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Bravo. Tu as nommé le goût. C'est du bon travail. Un bout reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1737,7 +1739,7 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé mâche.
+          <t>narrateur|Amir mâche.
 narrateur|Ça croque.
 narrateur|Il mâche encore.
 enfant-m|C'est sucré, papa.
@@ -1774,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Noé pose le morceau. Tu veux un peu d'eau ? Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. Merci, Noé. On range le panier, maintenant ? Oui. Noé aide. Tu as fini de ranger le panier ? Oui, papa. Bravo. Tu as bien aidé. La cuisine est calme. On reste un moment à table ? Noé reste avec papa. Le bout orange attend. La carotte ne s'échappe plus.</t>
+          <t>Amir pose le morceau. Tu veux un peu d'eau ? Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. Merci, Amir. On range le panier, maintenant ? Oui. Amir aide. Tu as fini de ranger le panier ? Oui, papa. Bravo. Tu as bien aidé. La cuisine est calme. On reste un moment à table ? Amir reste avec papa. Le bout orange attend. La carotte ne s'échappe plus.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1910,21 +1912,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Noé pose le morceau.
+          <t>narrateur|Amir pose le morceau.
 papa|Tu veux un peu d'eau ?
 narrateur|Il boit une gorgée d'eau.
 papa|Le reste peut attendre.
 enfant-m|Merci, papa.
-papa|Merci, Noé.
+papa|Merci, Amir.
 papa|On range le panier, maintenant ?
 enfant-m|Oui.
-narrateur|Noé aide.
+narrateur|Amir aide.
 papa|Tu as fini de ranger le panier ?
 enfant-m|Oui, papa.
 papa|Bravo. Tu as bien aidé.
 narrateur|La cuisine est calme.
 papa|On reste un moment à table ?
-narrateur|Noé reste avec papa.
+narrateur|Amir reste avec papa.
 narrateur|Le bout orange attend.
 narrateur|La carotte ne s'échappe plus.</t>
         </is>
@@ -1954,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Noé a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. Bravo, Noé. On était assis, ensemble. L'histoire est finie.</t>
+          <t>Amir a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. Bravo, Amir. On était assis, ensemble. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2094,10 +2096,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Noé a encore le croquant dans la bouche.
+          <t>narrateur|Amir a encore le croquant dans la bouche.
 enfant-m|C'était sucré.
 papa|Un petit morceau a suffi.
-papa|Bravo, Noé.
+papa|Bravo, Amir.
 papa|On était assis, ensemble.
 narrateur|L'histoire est finie.</t>
         </is>
@@ -2121,7 +2123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2201,6 +2203,13 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-NAR-008 récit captivant, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Ceci est l'histoire d'un petit panier. Le panier rentre du marché. Le village est encore tout frais. Il a plu, tout à l'heure. Les toits brillent. Amir marche avec papa. Leurs chaussures font clap, clap. Le panier est lourd, un peu. On le porte à deux ? Oui, papa. Ils arrivent dans la cuisine. L'évier sent le citron. On pose le panier sur la table ? Ils posent le panier. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Tu peux la rattraper, Amir. Amir se baisse. Il avance les deux mains. La carotte roule encore. Amir la suit. Il la rattrape. Elle est dans ses mains. Bravo, Amir ! Bien attrapé. Tu as fait du bon travail. La carotte est lisse et froide. Elle sent le marché. Ça sent le marché, papa. Oui. Un peu la terre. Un peu le soleil. Tu la poses près de l'évier ? Papa lave la carotte. L'eau coule. On la lave ensemble. Papa coupe un petit morceau. Viens t'asseoir. Amir s'assoit à table. Papa s'assoit aussi. Bravo. Tu es bien assis. On est ensemble. Le morceau est orange. Il brille un peu. Tu veux goûter ? Amir met le morceau dans sa bouche. Il goûte.</t>
+          <t>Ceci est l'histoire d'un petit panier. Le panier rentre du marché. Le village est encore tout frais. Il a plu, tout à l'heure. Les toits brillent. Amir marche avec papa. Leurs chaussures font clap, clap. Le panier est lourd, un peu. On le porte à deux ? Oui, papa. Ils arrivent dans la cuisine. L'évier sent le citron. On pose le panier sur la table ? Ils posent le panier. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Tu peux la rattraper, Amir. Amir se baisse. Il avance les deux mains. La carotte roule encore. Amir la suit. Il la rattrape. Elle est dans ses mains. Bravo, Amir ! Bien attrapé. La carotte est lisse et froide. Elle sent le marché. Ça sent le marché, papa. Oui. Un peu la terre. Un peu le soleil. Tu la poses près de l'évier ? Papa lave la carotte. L'eau coule. On la lave ensemble. Papa coupe un petit morceau. Viens t'asseoir. Amir s'assoit à table. Papa s'assoit aussi. Bravo. Tu es bien assis. On est ensemble. Le morceau est orange. Il brille un peu. Tu veux goûter ? Amir met le morceau dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé rentre du marché avec papa. Dans le panier, il y a des carottes orange. Papa les lave. Il coupe une petite carotte. Noé s'assoit à table. Papa dit : tu peux &lt;emphasis level="moderate"&gt;goûter&lt;/emphasis&gt;. Une petite portion, c'est assez. Noé prend une petite bouchée. Il mâche. C'est croquant. C'est un peu sucré. Noé va nommer le goût. Il dit à papa : c'est sucré et croquant. Papa sourit. Merci d'avoir goûté, dit papa. La petite portion reste dans l'assiette. Noé n'a pas besoin de tout finir. Il boit une gorgée d'eau. Papa range le reste. Noé a goûté. Il a dit le goût.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ceci est l'histoire d'un petit panier. Le panier rentre du marché. Le village est encore tout frais. Il a plu, tout à l'heure. Les toits brillent. Amir marche avec papa. Leurs chaussures font clap, clap. Le panier est lourd, un peu. On le porte à deux ? Oui, papa. Ils arrivent dans la cuisine. L'évier sent le citron. On pose le panier sur la table ? Ils posent le panier. Le panier est plein. Il penche un peu. Une carotte orange s'échappe. Elle roule vers le bord. Elle part ! Elle tombe par terre. Elle roule sous la table. Tu peux la rattraper, Amir. Amir se baisse. Il avance les deux mains. La carotte roule encore. Amir la suit. Il la rattrape. Elle est dans ses mains. Bravo, Amir ! Bien attrapé. La carotte est lisse et froide. Elle sent le marché. Ça sent le marché, papa. Oui. Un peu la terre. Un peu le soleil. Tu la poses près de l'évier ? Papa lave la carotte. L'eau coule. On la lave ensemble. Papa coupe un petit morceau. Viens t'asseoir. Amir s'assoit à table. Papa s'assoit aussi. Bravo. Tu es bien assis. On est ensemble. Le morceau est orange. Il brille un peu. Tu veux goûter ? Amir met le morceau dans sa bouche. Il goûte.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1359,7 +1359,6 @@
 narrateur|Elle est dans ses mains.
 papa|Bravo, Amir !
 papa|Bien attrapé.
-papa|Tu as fait du bon travail.
 narrateur|La carotte est lisse et froide.
 narrateur|Elle sent le marché.
 enfant-m|Ça sent le marché, papa.
@@ -1415,7 +1414,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Noé goûte la carotte. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir goûte. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,7 +1569,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1595,12 +1593,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amir mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Bravo. Tu as nommé le goût. C'est du bon travail. Un bout reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
+          <t>Amir mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Bravo. Tu as nommé le goût. Un bout reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé a goûté. Il a nommé le goût. Une &lt;emphasis level="moderate"&gt;petite&lt;/emphasis&gt; portion, c'est assez. Papa est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir mâche. Ça croque. Il mâche encore. C'est sucré, papa. C'est croquant. Oui. Sucré et croquant. Bravo. Tu as nommé le goût. Un bout reste dans l'assiette. Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1746,12 +1744,10 @@
 enfant-m|C'est croquant.
 papa|Oui. Sucré et croquant.
 papa|Bravo. Tu as nommé le goût.
-papa|C'est du bon travail.
 narrateur|Un bout reste dans l'assiette.
 papa|Tu as fini ta petite bouchée ?</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1781,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Noé range sa chaise. La carotte reste à sa place. Merci, dit Noé.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir pose le morceau. Tu veux un peu d'eau ? Il boit une gorgée d'eau. Le reste peut attendre. Merci, papa. Merci, Amir. On range le panier, maintenant ? Oui. Amir aide. Tu as fini de ranger le panier ? Oui, papa. Bravo. Tu as bien aidé. La cuisine est calme. On reste un moment à table ? Amir reste avec papa. Le bout orange attend. La carotte ne s'échappe plus.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1931,7 +1927,6 @@
 narrateur|La carotte ne s'échappe plus.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1956,12 +1951,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Amir a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. Bravo, Amir. On était assis, ensemble. L'histoire est finie.</t>
+          <t>Amir a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. Bravo, Amir. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a encore le croquant dans la bouche. C'était sucré. Un petit morceau a suffi. Bravo, Amir. On était assis, ensemble.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2100,11 +2095,9 @@
 enfant-m|C'était sucré.
 papa|Un petit morceau a suffi.
 papa|Bravo, Amir.
-papa|On était assis, ensemble.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+papa|On était assis, ensemble.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2123,7 +2116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2210,6 +2203,13 @@
       <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
+++ b/stories/arbres/ATOM-SAN.ALI.001-02.xlsx
@@ -688,7 +688,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Noé, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>
